--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_5_сценарная_оценка_Similarweb_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_5_сценарная_оценка_Similarweb_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-89518d\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C71EB3-8020-475A-8E64-828660E43C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F931BFA6-EDF8-40FF-BFD0-48D38580B417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="312">
   <si>
     <t>Методика сценарной оценки рынка с учетом данных Similarweb: расчетный Excel-шаблон</t>
   </si>
@@ -782,9 +782,6 @@
     <t>Сайты конкурентов</t>
   </si>
   <si>
-    <t>[вставить URL]</t>
-  </si>
-  <si>
     <t>Прайсы, услуги, средний чек, позиционирование</t>
   </si>
   <si>
@@ -975,6 +972,12 @@
   </si>
   <si>
     <t>Снизу вверх (книга 2): SAM x доля SOM, EUR/год</t>
+  </si>
+  <si>
+    <t>perfectxl.com/pricing; arixcel.com/pricing; shortcut.ai/pricing; rows.com/pricing</t>
+  </si>
+  <si>
+    <t>https://trends.google.com/ ; https://wordstat.yandex.ru/ (выгрузки ЛР1)</t>
   </si>
 </sst>
 </file>
@@ -2910,7 +2913,7 @@
         <v>79</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>80</v>
@@ -2939,7 +2942,7 @@
         <v>84</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>80</v>
@@ -2968,7 +2971,7 @@
         <v>87</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>80</v>
@@ -3029,13 +3032,13 @@
         <v>19.43</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>81</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>95</v>
@@ -3058,7 +3061,7 @@
         <v>5.1749999999999998</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>81</v>
@@ -3255,7 +3258,7 @@
         <v>2.5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>120</v>
@@ -4255,13 +4258,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>262</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>263</v>
       </c>
       <c r="E5" s="14">
         <v>154111</v>
@@ -4288,10 +4291,10 @@
         <v>0.1395631262304261</v>
       </c>
       <c r="L5" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -4301,13 +4304,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="D6" s="13" t="s">
         <v>267</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>268</v>
       </c>
       <c r="E6" s="14">
         <v>35325</v>
@@ -4334,10 +4337,10 @@
         <v>0.12108744755929404</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -4347,13 +4350,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="13" t="s">
         <v>271</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>272</v>
       </c>
       <c r="E7" s="14">
         <v>241737</v>
@@ -4380,10 +4383,10 @@
         <v>3.8568009505722582E-2</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -4393,13 +4396,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="D8" s="13" t="s">
         <v>275</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>276</v>
       </c>
       <c r="E8" s="14">
         <v>202178</v>
@@ -4426,10 +4429,10 @@
         <v>9.5912252032267081E-2</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -4439,13 +4442,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="D9" s="13" t="s">
         <v>279</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>280</v>
       </c>
       <c r="E9" s="14">
         <v>14688</v>
@@ -4472,10 +4475,10 @@
         <v>6.4677401436614573E-2</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -4485,13 +4488,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>283</v>
-      </c>
       <c r="D10" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E10" s="14">
         <v>17824</v>
@@ -4518,10 +4521,10 @@
         <v>7.6815062787950403E-2</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -4531,13 +4534,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>286</v>
-      </c>
       <c r="D11" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E11" s="14">
         <v>292214</v>
@@ -4564,10 +4567,10 @@
         <v>7.7622698437054938E-2</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -4577,13 +4580,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>289</v>
-      </c>
       <c r="D12" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E12" s="14">
         <v>116617</v>
@@ -4610,10 +4613,10 @@
         <v>5.1815134517398685E-2</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -4623,13 +4626,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>292</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>293</v>
       </c>
       <c r="E13" s="14">
         <v>222359</v>
@@ -4656,10 +4659,10 @@
         <v>0.26290785536507233</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -4669,13 +4672,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
         <v>296</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>297</v>
       </c>
       <c r="E14" s="14">
         <v>701540</v>
@@ -4702,10 +4705,10 @@
         <v>5.6083405697148821E-2</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -4715,13 +4718,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>300</v>
-      </c>
       <c r="D15" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E15" s="14">
         <v>1935</v>
@@ -4748,10 +4751,10 @@
         <v>9.5301615493707404E-3</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -4761,13 +4764,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="13" t="s">
         <v>303</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>304</v>
       </c>
       <c r="E16" s="14">
         <v>5522</v>
@@ -4794,10 +4797,10 @@
         <v>5.417444881679636E-3</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -8089,7 +8092,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -9384,7 +9387,7 @@
     </row>
     <row r="6" spans="1:15" ht="25.5">
       <c r="A6" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B6" s="20">
         <f>'05_Платформа'!K5</f>
@@ -9414,7 +9417,7 @@
     </row>
     <row r="7" spans="1:15" ht="38.25">
       <c r="A7" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B7" s="19">
         <v>103</v>
@@ -9441,7 +9444,7 @@
     </row>
     <row r="8" spans="1:15" ht="25.5">
       <c r="A8" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B8" s="19">
         <v>5040</v>
@@ -9468,7 +9471,7 @@
     </row>
     <row r="9" spans="1:15" ht="25.5">
       <c r="A9" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B9" s="19">
         <v>10501</v>
@@ -9627,7 +9630,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="25.5">
+    <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
         <v>202</v>
       </c>
@@ -11707,7 +11710,7 @@
         <v>232</v>
       </c>
       <c r="E4" s="24">
-        <v>46145</v>
+        <v>46298</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>233</v>
@@ -11738,7 +11741,7 @@
         <v>237</v>
       </c>
       <c r="E5" s="24">
-        <v>46145</v>
+        <v>46298</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>238</v>
@@ -11769,7 +11772,7 @@
         <v>242</v>
       </c>
       <c r="E6" s="24">
-        <v>46145</v>
+        <v>46298</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>243</v>
@@ -11786,7 +11789,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" ht="25.5">
       <c r="A7" s="8">
         <v>4</v>
       </c>
@@ -11794,19 +11797,19 @@
         <v>245</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="24">
+        <v>46298</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E7" s="24">
-        <v>46145</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -11817,27 +11820,27 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" ht="25.5">
       <c r="A8" s="8">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="24">
+        <v>46298</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E8" s="24">
-        <v>46145</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_5_сценарная_оценка_Similarweb_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_5_сценарная_оценка_Similarweb_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C71EB3-8020-475A-8E64-828660E43C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86B71C8-C3AC-4B75-8F2B-FC9720A13D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="07_Дашборд" sheetId="8" r:id="rId8"/>
     <sheet name="08_Источники" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1236,7 +1236,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-86A7-4014-8C28-E42EDAFEC353}"/>
+              <c16:uniqueId val="{00000000-F51F-4C7C-9B26-2013D6B04DAD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_5_сценарная_оценка_Similarweb_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_5_сценарная_оценка_Similarweb_TableMind.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86B71C8-C3AC-4B75-8F2B-FC9720A13D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B4783E-0AD0-425E-A1A2-C4E4A48D4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1236,7 +1236,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F51F-4C7C-9B26-2013D6B04DAD}"/>
+              <c16:uniqueId val="{00000000-8BE3-4187-992A-FC4D5307F23C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
